--- a/frontend/public/templates/projects-import-template.xlsx
+++ b/frontend/public/templates/projects-import-template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,11 +29,7 @@
     <font>
       <b val="1"/>
       <color rgb="001F3D2B"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="0000873C"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
@@ -53,7 +49,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -61,35 +57,19 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00E5E7EB"/>
-      </left>
-      <right style="thin">
-        <color rgb="00E5E7EB"/>
-      </right>
-      <top style="thin">
-        <color rgb="00E5E7EB"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00E5E7EB"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -457,10 +437,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="105" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -478,30 +458,23 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>1. 第二个 sheet 的列与“门户内容 - 科研项目 - 新增项目”表单对应，请从第 2 行开始填写。</t>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>1. 项目名称必填；项目编号用于自动去重。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>2. 必填：项目名称。系统优先按项目编号更新已有项目；项目编号为空时按项目名称匹配。</t>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2. 状态可直接写项目负责人、课题负责人、项目骨干、参与等。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>3. 门户展示建议保留项目方向、资助来源、负责人和状态，不必填写敏感细节。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>4. 日期格式建议使用 YYYY-MM-DD。</t>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>3. 首页排序默认 0。</t>
         </is>
       </c>
     </row>
@@ -516,129 +489,131 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="58" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>项目名称</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>项目编号</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>资助来源</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>开始日期</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>结束日期</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>经费</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>状态</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>开始日期</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>结束日期</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="3" t="inlineStr">
         <is>
           <t>可见范围</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="3" t="inlineStr">
         <is>
           <t>首页排序</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>有机废弃物资源化与堆肥过程调控研究</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>项目编号示例</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
-        <is>
-          <t>国家级/省部级科研项目</t>
-        </is>
-      </c>
-      <c r="D2" s="5" t="inlineStr">
-        <is>
-          <t>团队负责人</t>
-        </is>
-      </c>
-      <c r="E2" s="5" t="inlineStr">
-        <is>
-          <t>在研</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>国家自然科学基金委员会</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>魏雨泉</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>2028-12-31</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>项目负责人</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>公开</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
-        <is>
-          <t>门户展示版说明。</t>
-        </is>
-      </c>
-      <c r="J2" s="5" t="n">
-        <v>10</v>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>简短说明即可。</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="H2:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"公开,成员可见,管理员可见"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/frontend/public/templates/projects-import-template.xlsx
+++ b/frontend/public/templates/projects-import-template.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,7 +29,11 @@
     <font>
       <b val="1"/>
       <color rgb="001F3D2B"/>
-      <sz val="14"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0000873C"/>
     </font>
     <font>
       <b val="1"/>
@@ -49,7 +53,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -57,19 +61,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -437,10 +457,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="110" customWidth="1" min="1" max="1"/>
+    <col width="105" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,23 +478,37 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>1. 项目名称必填；项目编号用于自动去重。</t>
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>1. 第二个 sheet 的列与“门户内容 - 科研项目 - 新增项目”表单对应，请从第 2 行开始填写。</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2. 状态可直接写项目负责人、课题负责人、项目骨干、参与等。</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2. 必填：项目名称。系统优先按项目编号更新已有项目；项目编号为空时按项目名称匹配。</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>3. 首页排序默认 0。</t>
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>3. 经费为可选字段，不需要公开展示时可留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>4. 首页排序：0 表示不在首页展示；大于 0 时按数字从小到大展示。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>5. 日期格式建议使用 YYYY-MM-DD。</t>
         </is>
       </c>
     </row>
@@ -492,128 +526,133 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="58" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>项目名称</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>项目编号</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>资助来源</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>负责人</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>开始日期</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>结束日期</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>经费</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>状态</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>可见范围</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>首页排序</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>有机废弃物资源化与堆肥过程调控研究</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>项目编号示例</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>国家自然科学基金委员会</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>魏雨泉</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>国家级/省部级科研项目</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>团队负责人</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>在研</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>2028-12-31</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>项目负责人</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>公开</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>简短说明即可。</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0</v>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>门户展示版说明。</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="I2:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"公开,成员可见,管理员可见"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>